--- a/XLS-003 - Open Questions Register - v0.2.xlsx
+++ b/XLS-003 - Open Questions Register - v0.2.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="10" customWidth="1" style="7" min="1" max="1"/>
@@ -481,7 +481,7 @@
     <row r="2" ht="15" customHeight="1" s="8">
       <c r="A2" s="10" t="inlineStr">
         <is>
-          <t>PMOC Software | Fase 1 | v0.2 DRAFT | 22/09/2026 | Origem das alterações: Services.NET Phase 1 Audit — Approved | Status: aguardando segunda revisão formal da Services.NET | Questão sem resposta não pode ser substituída por suposição.</t>
+          <t>PMOC Software | Fase 1 | v0.2 — APPROVED | 22/09/2026 | Origem das alterações: Services.NET Phase 1 Audit — Approved; Services.NET segunda revisão formal da Fase 1 v0.2 | Status: APPROVED WITH OPEN ACTIONS — Fase 1 aprovada formalmente pela Services.NET em 22/09/2026; Fase 2 não iniciada | Questão sem resposta não pode ser substituída por suposição.</t>
         </is>
       </c>
     </row>
@@ -593,7 +593,7 @@
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>Quem é o patrocinador formal do projeto?</t>
+          <t>ENCERRADA — Patrocinador formal definido: Alan Maciel Lima, CEO e especialista da Services.NET.</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
@@ -603,7 +603,7 @@
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>Autoridade de aprovação da Fase 1</t>
+          <t>Autoridade de aprovação executiva da Fase 1 atendida</t>
         </is>
       </c>
       <c r="F6" s="12" t="inlineStr">
@@ -613,17 +613,17 @@
       </c>
       <c r="G6" s="12" t="inlineStr">
         <is>
-          <t>Aberta</t>
+          <t>Respondida/Encerrada</t>
         </is>
       </c>
       <c r="H6" s="12" t="inlineStr">
         <is>
-          <t>Bloqueia aprovação formal</t>
+          <t>Responsabilidades registradas: direção, gestão, planejamento, supervisão da execução e aprovação executiva do projeto.</t>
         </is>
       </c>
       <c r="I6" s="12" t="inlineStr">
         <is>
-          <t>v0.1</t>
+          <t>v0.2 — encerrada na formalização final da Fase 1</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>Quem exerce o papel de Product Owner?</t>
+          <t>ENCERRADA — Product Owner institucional definido: Services.NET.</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>Priorização e aceite</t>
+          <t>Priorização e aceite passam a ter autoridade institucional definida</t>
         </is>
       </c>
       <c r="F7" s="12" t="inlineStr">
@@ -660,17 +660,17 @@
       </c>
       <c r="G7" s="12" t="inlineStr">
         <is>
-          <t>Aberta</t>
+          <t>Respondida/Encerrada</t>
         </is>
       </c>
       <c r="H7" s="12" t="inlineStr">
         <is>
-          <t>Bloqueia backlog</t>
+          <t>Quando um campo exigir pessoa física: "Services.NET — autoridade institucional; representante operacional a ser designado conforme necessidade". A Clima Zero não é proprietária do produto nem autoridade exclusiva sobre roadmap.</t>
         </is>
       </c>
       <c r="I7" s="12" t="inlineStr">
         <is>
-          <t>v0.1</t>
+          <t>v0.2 — encerrada na formalização final da Fase 1</t>
         </is>
       </c>
     </row>
@@ -969,7 +969,7 @@
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t>O contexto de origem confirma a existência de um cliente candidato/piloto que motivou a plataforma; quais são a identidade formal do tenant-piloto, interlocutores, disponibilidade para levantamento, compromisso de operar o MVP e agenda da Fase 2?</t>
+          <t>ENCERRADA quanto à existência e identidade do tenant-piloto: Clima Zero Climatização.</t>
         </is>
       </c>
       <c r="D14" s="12" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="E14" s="12" t="inlineStr">
         <is>
-          <t>Sem identidade formal, interlocutores e compromisso operacional, a Fase 2 não possui fonte primária governada</t>
+          <t>Fonte primária do levantamento identificada</t>
         </is>
       </c>
       <c r="F14" s="12" t="inlineStr">
@@ -989,17 +989,17 @@
       </c>
       <c r="G14" s="12" t="inlineStr">
         <is>
-          <t>Aberta</t>
+          <t>Respondida/Encerrada</t>
         </is>
       </c>
       <c r="H14" s="12" t="inlineStr">
         <is>
-          <t>Reformulada por Codex: existência de cliente candidato/piloto confirmada pelo contexto; detalhes formais permanecem pendentes</t>
+          <t>Clima Zero Climatização é empresa parceira que apresentou à Services.NET a necessidade da plataforma. Será fonte primária de processos, validação de necessidades operacionais, documentos/formulários atuais, regras de campo, testes e validação do MVP quando acordado. Interlocutores, disponibilidade e agenda seguem em OQ-022.</t>
         </is>
       </c>
       <c r="I14" s="12" t="inlineStr">
         <is>
-          <t>v0.2 — reformulada por Codex</t>
+          <t>v0.2 — encerrada na formalização final da Fase 1</t>
         </is>
       </c>
     </row>
@@ -1517,6 +1517,53 @@
       <c r="I25" s="13" t="inlineStr">
         <is>
           <t>v0.2 — reformulada por Codex</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="57.45" customHeight="1" s="8">
+      <c r="A26" s="13" t="inlineStr">
+        <is>
+          <t>OQ-022</t>
+        </is>
+      </c>
+      <c r="B26" s="13" t="inlineStr">
+        <is>
+          <t>Operação</t>
+        </is>
+      </c>
+      <c r="C26" s="13" t="inlineStr">
+        <is>
+          <t>Quais interlocutores específicos da Clima Zero Climatização, disponibilidade para levantamento, compromisso de operar/validar o MVP e agenda da Fase 2 serão formalizados?</t>
+        </is>
+      </c>
+      <c r="D26" s="13" t="inlineStr">
+        <is>
+          <t>Product Owner institucional (STK-002) + Clima Zero Climatização (STK-010)</t>
+        </is>
+      </c>
+      <c r="E26" s="13" t="inlineStr">
+        <is>
+          <t>Sem interlocutores e agenda, a Fase 2 não possui base operacional governada, embora a identidade do tenant-piloto esteja encerrada em OQ-010</t>
+        </is>
+      </c>
+      <c r="F26" s="13" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="G26" s="13" t="inlineStr">
+        <is>
+          <t>Aberta</t>
+        </is>
+      </c>
+      <c r="H26" s="13" t="inlineStr">
+        <is>
+          <t>Criada para separar pendências operacionais da identidade/existência do tenant-piloto; não reabre OQ-010.</t>
+        </is>
+      </c>
+      <c r="I26" s="13" t="inlineStr">
+        <is>
+          <t>v0.2 — criada na formalização final da Fase 1</t>
         </is>
       </c>
     </row>
@@ -1565,6 +1612,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="15" customHeight="1" s="8">
       <c r="A4" s="14" t="inlineStr">
         <is>
@@ -1616,17 +1664,17 @@
         </is>
       </c>
       <c r="B8" s="14" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" s="8">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>Esperado — abertas após Codex</t>
+          <t>Esperado — abertas após formalização final</t>
         </is>
       </c>
       <c r="B9" s="14" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" s="8">
@@ -1636,7 +1684,7 @@
         </is>
       </c>
       <c r="B10" s="14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" s="8">
@@ -1650,13 +1698,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Encerradas por Codex</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1</v>
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>Encerradas/respondidas após formalização final</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="n">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
